--- a/ExcelData/TableHero.xlsx
+++ b/ExcelData/TableHero.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\Mole_Fork\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B7DF8B-FB8C-458E-A824-F92A7DC14852}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF39AE36-5153-4ACF-BD06-7D9DC94BF910}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NPC" sheetId="1" r:id="rId1"/>
     <sheet name="Hero" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -81,6 +81,10 @@
   </si>
   <si>
     <t>#TableHero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -133,7 +137,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -144,6 +148,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -426,117 +436,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2">
-        <v>1000001</v>
-      </c>
-      <c r="C2" t="s">
+        <v>10000</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>11</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <f>_xlfn.CONCAT(B2,0)</f>
+        <v>100000</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <f>_xlfn.CONCAT(B2,1)</f>
+        <v>100001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>1000002</v>
-      </c>
-      <c r="C3" t="s">
+        <v>10001</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3">
-        <v>100</v>
-      </c>
-      <c r="G3">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <f t="shared" ref="G3:G5" si="0">_xlfn.CONCAT(B3,0)</f>
+        <v>100010</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <f t="shared" ref="H3:H5" si="1">_xlfn.CONCAT(B3,1)</f>
+        <v>100011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>1000003</v>
-      </c>
-      <c r="C4" t="s">
+        <v>10002</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>134</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>100020</v>
+      </c>
+      <c r="H4" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>100021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>1000004</v>
-      </c>
-      <c r="C5" t="s">
+        <v>10003</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>20</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
       <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>100030</v>
+      </c>
+      <c r="H5" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>100031</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -546,117 +579,142 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="9" style="5"/>
+    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2">
-        <v>2000001</v>
-      </c>
-      <c r="C2" t="s">
+        <v>20000</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>11</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <f>_xlfn.CONCAT(B2,0)</f>
+        <v>200000</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <f>_xlfn.CONCAT(B2,1)</f>
+        <v>200001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>2000002</v>
-      </c>
-      <c r="C3" t="s">
+        <v>20001</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3">
-        <v>100</v>
-      </c>
-      <c r="G3">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <f t="shared" ref="G3:G5" si="0">_xlfn.CONCAT(B3,0)</f>
+        <v>200010</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <f t="shared" ref="H3:H5" si="1">_xlfn.CONCAT(B3,1)</f>
+        <v>200011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>2000003</v>
-      </c>
-      <c r="C4" t="s">
+        <v>20002</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>134</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>200020</v>
+      </c>
+      <c r="H4" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>200021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>2000004</v>
-      </c>
-      <c r="C5" t="s">
+        <v>20003</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>20</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
       <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>200030</v>
+      </c>
+      <c r="H5" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>200031</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelData/TableHero.xlsx
+++ b/ExcelData/TableHero.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\Mole_Fork\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF39AE36-5153-4ACF-BD06-7D9DC94BF910}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621F15D2-15D0-4480-8F80-E0CD0662A39F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="NPC" sheetId="1" r:id="rId1"/>
-    <sheet name="Hero" sheetId="2" r:id="rId2"/>
+    <sheet name="NOTE" sheetId="3" r:id="rId1"/>
+    <sheet name="Hero" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -36,34 +36,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ENABLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILLS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NAME_TID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>민수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영희</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>병기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이순신</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -85,6 +61,42 @@
   </si>
   <si>
     <t>TYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PREFAB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RADIUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LEVEL_GROUP_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILLS[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEYWORDS[]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -123,12 +135,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -137,23 +164,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -435,286 +459,316 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF9EF42-3C21-4746-A0FC-AACDB5F1F160}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B2">
-        <v>10000</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <f>_xlfn.CONCAT(B2,0)</f>
-        <v>100000</v>
-      </c>
-      <c r="H2" s="5" t="str">
-        <f>_xlfn.CONCAT(B2,1)</f>
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B3">
-        <v>10001</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <f t="shared" ref="G3:G5" si="0">_xlfn.CONCAT(B3,0)</f>
-        <v>100010</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <f t="shared" ref="H3:H5" si="1">_xlfn.CONCAT(B3,1)</f>
-        <v>100011</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>10002</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>134</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>100020</v>
-      </c>
-      <c r="H4" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>100021</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>10003</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>100030</v>
-      </c>
-      <c r="H5" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>100031</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G1:H1"/>
-  </mergeCells>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="10.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="17.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="20" width="5.625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B2" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>10000</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>10001</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="4"/>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>10000</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>10001</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B2">
-        <v>20000</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <f>_xlfn.CONCAT(B2,0)</f>
-        <v>200000</v>
-      </c>
-      <c r="H2" s="5" t="str">
-        <f>_xlfn.CONCAT(B2,1)</f>
-        <v>200001</v>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>134</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>10000</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>10001</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B3">
-        <v>20001</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <f t="shared" ref="G3:G5" si="0">_xlfn.CONCAT(B3,0)</f>
-        <v>200010</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <f t="shared" ref="H3:H5" si="1">_xlfn.CONCAT(B3,1)</f>
-        <v>200011</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>20002</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>134</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>200020</v>
-      </c>
-      <c r="H4" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>200021</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>20003</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
         <v>20</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>200030</v>
-      </c>
-      <c r="H5" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>200031</v>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>10000</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>10001</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G1:H1"/>
+  <mergeCells count="2">
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="K1:O1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelData/TableHero.xlsx
+++ b/ExcelData/TableHero.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\Mole_Fork\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621F15D2-15D0-4480-8F80-E0CD0662A39F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE74ED1-E613-4AF8-A243-ED8FEF9F3A6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -97,6 +97,38 @@
   </si>
   <si>
     <t>KEYWORDS[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STATS[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Health</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Energy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Strength</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Dexterity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Intelligence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Weight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +196,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -179,6 +211,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,7 +508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
@@ -483,7 +521,7 @@
     <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -514,89 +552,81 @@
       <c r="J1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3" t="s">
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B2" s="1">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
         <v>10000</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>10000</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>10001</v>
-      </c>
-      <c r="R2" s="1">
-        <v>0</v>
-      </c>
-      <c r="S2" s="1">
-        <v>0</v>
-      </c>
-      <c r="T2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -611,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -646,16 +676,37 @@
       <c r="T3" s="1">
         <v>0</v>
       </c>
+      <c r="U3" s="1">
+        <v>10</v>
+      </c>
+      <c r="V3" s="1">
+        <v>10</v>
+      </c>
+      <c r="W3" s="1">
+        <v>10</v>
+      </c>
+      <c r="X3" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -670,7 +721,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -705,16 +756,37 @@
       <c r="T4" s="1">
         <v>0</v>
       </c>
+      <c r="U4" s="1">
+        <v>10</v>
+      </c>
+      <c r="V4" s="1">
+        <v>10</v>
+      </c>
+      <c r="W4" s="1">
+        <v>10</v>
+      </c>
+      <c r="X4" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -729,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -763,6 +835,107 @@
       </c>
       <c r="T5" s="1">
         <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>10</v>
+      </c>
+      <c r="V5" s="1">
+        <v>10</v>
+      </c>
+      <c r="W5" s="1">
+        <v>10</v>
+      </c>
+      <c r="X5" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>20</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>10000</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>10001</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>10</v>
+      </c>
+      <c r="V6" s="1">
+        <v>10</v>
+      </c>
+      <c r="W6" s="1">
+        <v>10</v>
+      </c>
+      <c r="X6" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/TableHero.xlsx
+++ b/ExcelData/TableHero.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\Mole_Fork\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE74ED1-E613-4AF8-A243-ED8FEF9F3A6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F33974D-CF56-4084-95A2-D5E54F6D750C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,22 +40,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이순신</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>류관순</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이문세</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정관장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#TableHero</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,10 +68,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LEVEL_GROUP_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,10 +84,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>!Health</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>!Energy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,10 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>!Dexterity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>!Intelligence</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,7 +100,130 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>!Agility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Stamina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Immunity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Depression</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Anxiety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Concentration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Happiness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Fatigue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Creativity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Hostility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Motivation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Memory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Loneliness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Belonging</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SelfEsteem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!BeingLoved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!BeingRecognized</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Safety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Comfort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Cleanliness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Naturalness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ResourceAbundance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Stress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름_10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름_10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름_10002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름_10003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>!Weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Prefab/Hero/Character_10000.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Prefab/Hero/Character_10001.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Prefab/Hero/Character_10002.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Prefab/Hero/Character_10003.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -153,7 +248,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,6 +258,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -196,7 +315,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -212,11 +331,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,75 +639,120 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="1"/>
     <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="10.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="17.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="20" width="5.625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
+    <col min="21" max="22" width="9" style="1"/>
+    <col min="23" max="23" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="9" style="1"/>
+    <col min="29" max="29" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9" style="1"/>
+    <col min="39" max="40" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9" style="1"/>
+    <col min="46" max="46" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -596,29 +772,92 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="AA2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="AB2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="AD2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="AF2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="AG2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AH2" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="AI2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AS2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AV2" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>10000</v>
       </c>
@@ -626,16 +865,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
@@ -677,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="U3" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="V3" s="1">
         <v>10</v>
@@ -697,8 +936,71 @@
       <c r="AA3" s="1">
         <v>1</v>
       </c>
+      <c r="AB3" s="1">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -706,19 +1008,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1">
         <v>12</v>
@@ -757,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="V4" s="1">
         <v>10</v>
@@ -777,8 +1079,71 @@
       <c r="AA4" s="1">
         <v>1</v>
       </c>
+      <c r="AB4" s="1">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -786,19 +1151,19 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H5" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1">
         <v>134</v>
@@ -837,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V5" s="1">
         <v>10</v>
@@ -857,8 +1222,71 @@
       <c r="AA5" s="1">
         <v>1</v>
       </c>
+      <c r="AB5" s="1">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -866,19 +1294,19 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" s="1">
         <v>20</v>
@@ -917,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V6" s="1">
         <v>10</v>
@@ -936,6 +1364,69 @@
       </c>
       <c r="AA6" s="1">
         <v>1</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/TableHero.xlsx
+++ b/ExcelData/TableHero.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\Mole_Fork\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F33974D-CF56-4084-95A2-D5E54F6D750C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839C8B3B-46E5-476C-9D72-601B67C02824}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTE" sheetId="3" r:id="rId1"/>
     <sheet name="Hero" sheetId="1" r:id="rId2"/>
+    <sheet name="Monster" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="52">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -224,6 +225,14 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Prefab/Hero/Character_10003.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Prefab/Hero/Character_20000.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹색괴물</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -315,7 +324,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -345,6 +354,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -707,20 +719,20 @@
       <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10" t="s">
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
       <c r="U1" s="5" t="s">
         <v>13</v>
       </c>
@@ -1438,4 +1450,347 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE02A215-8D3D-4010-968D-B171412A9E2D}">
+  <dimension ref="A1:AV3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="59.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+    </row>
+    <row r="2" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AS2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AV2" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>20000</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>20001</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1">
+        <v>10</v>
+      </c>
+      <c r="W3" s="1">
+        <v>10</v>
+      </c>
+      <c r="X3" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="P1:T1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>